--- a/scenario réaliste/ARC_reel_sans_inv.xlsx
+++ b/scenario réaliste/ARC_reel_sans_inv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\scenario réaliste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F2BDB7-0BF7-482F-97FF-5C14519E886D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4200248-3EB5-4E62-ABFF-7FE4FB9FB525}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="2" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="5" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
   </bookViews>
   <sheets>
     <sheet name="mun" sheetId="3" r:id="rId1"/>
@@ -3098,6 +3098,7 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="22.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
